--- a/artfynd/A 45937-2023 artfynd.xlsx
+++ b/artfynd/A 45937-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839411</v>
+        <v>119839408</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>79643</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>6464</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548284</v>
+        <v>548269</v>
       </c>
       <c r="R3" t="n">
-        <v>6962633</v>
+        <v>6962621</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839407</v>
+        <v>119839411</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90846</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548281</v>
+        <v>548284</v>
       </c>
       <c r="R4" t="n">
-        <v>6962549</v>
+        <v>6962633</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839409</v>
+        <v>119839407</v>
       </c>
       <c r="B5" t="n">
-        <v>79607</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +997,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548269</v>
+        <v>548281</v>
       </c>
       <c r="R5" t="n">
-        <v>6962621</v>
+        <v>6962549</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839410</v>
+        <v>119839409</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548277</v>
+        <v>548269</v>
       </c>
       <c r="R6" t="n">
-        <v>6962656</v>
+        <v>6962621</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1159,11 +1159,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1185,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839408</v>
+        <v>119839410</v>
       </c>
       <c r="B7" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1197,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1225,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548269</v>
+        <v>548277</v>
       </c>
       <c r="R7" t="n">
-        <v>6962621</v>
+        <v>6962656</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1266,6 +1261,11 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC7" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45937-2023 artfynd.xlsx
+++ b/artfynd/A 45937-2023 artfynd.xlsx
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839408</v>
+        <v>119839411</v>
       </c>
       <c r="B3" t="n">
-        <v>79643</v>
+        <v>90846</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -789,25 +789,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548269</v>
+        <v>548284</v>
       </c>
       <c r="R3" t="n">
-        <v>6962621</v>
+        <v>6962633</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839411</v>
+        <v>119839407</v>
       </c>
       <c r="B4" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548284</v>
+        <v>548281</v>
       </c>
       <c r="R4" t="n">
-        <v>6962633</v>
+        <v>6962549</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839407</v>
+        <v>119839408</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>79643</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>6464</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548281</v>
+        <v>548269</v>
       </c>
       <c r="R5" t="n">
-        <v>6962549</v>
+        <v>6962621</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1083,10 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839409</v>
+        <v>119839410</v>
       </c>
       <c r="B6" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1099,21 +1099,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1123,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548269</v>
+        <v>548277</v>
       </c>
       <c r="R6" t="n">
-        <v>6962621</v>
+        <v>6962656</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1159,6 +1159,11 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1185,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839410</v>
+        <v>119839409</v>
       </c>
       <c r="B7" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1201,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1225,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548277</v>
+        <v>548269</v>
       </c>
       <c r="R7" t="n">
-        <v>6962656</v>
+        <v>6962621</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>
@@ -1261,11 +1266,6 @@
       <c r="AA7" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 45937-2023 artfynd.xlsx
+++ b/artfynd/A 45937-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839413</v>
+        <v>119839409</v>
       </c>
       <c r="B2" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548277</v>
+        <v>548269</v>
       </c>
       <c r="R2" t="n">
-        <v>6962630</v>
+        <v>6962621</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839411</v>
+        <v>119839407</v>
       </c>
       <c r="B3" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548284</v>
+        <v>548281</v>
       </c>
       <c r="R3" t="n">
-        <v>6962633</v>
+        <v>6962549</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839407</v>
+        <v>119839413</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>90562</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -895,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>5432</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548281</v>
+        <v>548277</v>
       </c>
       <c r="R4" t="n">
-        <v>6962549</v>
+        <v>6962630</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839408</v>
+        <v>119839410</v>
       </c>
       <c r="B5" t="n">
-        <v>79643</v>
+        <v>57310</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -993,25 +993,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6464</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1021,10 +1021,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548269</v>
+        <v>548277</v>
       </c>
       <c r="R5" t="n">
-        <v>6962621</v>
+        <v>6962656</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1057,6 +1057,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1083,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839410</v>
+        <v>119839408</v>
       </c>
       <c r="B6" t="n">
-        <v>57310</v>
+        <v>79643</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1095,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>6464</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1123,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548277</v>
+        <v>548269</v>
       </c>
       <c r="R6" t="n">
-        <v>6962656</v>
+        <v>6962621</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1159,11 +1164,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839409</v>
+        <v>119839411</v>
       </c>
       <c r="B7" t="n">
-        <v>79607</v>
+        <v>90846</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548269</v>
+        <v>548284</v>
       </c>
       <c r="R7" t="n">
-        <v>6962621</v>
+        <v>6962633</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 45937-2023 artfynd.xlsx
+++ b/artfynd/A 45937-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839409</v>
+        <v>119839407</v>
       </c>
       <c r="B2" t="n">
-        <v>79607</v>
+        <v>90598</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548269</v>
+        <v>548281</v>
       </c>
       <c r="R2" t="n">
-        <v>6962621</v>
+        <v>6962549</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839407</v>
+        <v>119839411</v>
       </c>
       <c r="B3" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548281</v>
+        <v>548284</v>
       </c>
       <c r="R3" t="n">
-        <v>6962549</v>
+        <v>6962633</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -879,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839413</v>
+        <v>119839408</v>
       </c>
       <c r="B4" t="n">
-        <v>90562</v>
+        <v>79659</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +891,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +919,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548277</v>
+        <v>548269</v>
       </c>
       <c r="R4" t="n">
-        <v>6962630</v>
+        <v>6962621</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -984,7 +984,7 @@
         <v>119839410</v>
       </c>
       <c r="B5" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839408</v>
+        <v>119839409</v>
       </c>
       <c r="B6" t="n">
-        <v>79643</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1100,25 +1100,25 @@
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839411</v>
+        <v>119839413</v>
       </c>
       <c r="B7" t="n">
-        <v>90846</v>
+        <v>90580</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1206,21 +1206,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548284</v>
+        <v>548277</v>
       </c>
       <c r="R7" t="n">
-        <v>6962633</v>
+        <v>6962630</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 45937-2023 artfynd.xlsx
+++ b/artfynd/A 45937-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839407</v>
+        <v>119839411</v>
       </c>
       <c r="B2" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548281</v>
+        <v>548284</v>
       </c>
       <c r="R2" t="n">
-        <v>6962549</v>
+        <v>6962633</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839411</v>
+        <v>119839407</v>
       </c>
       <c r="B3" t="n">
-        <v>90864</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>658</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548284</v>
+        <v>548281</v>
       </c>
       <c r="R3" t="n">
-        <v>6962633</v>
+        <v>6962549</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>

--- a/artfynd/A 45937-2023 artfynd.xlsx
+++ b/artfynd/A 45937-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839411</v>
+        <v>119839409</v>
       </c>
       <c r="B2" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +715,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>548284</v>
+        <v>548269</v>
       </c>
       <c r="R2" t="n">
-        <v>6962633</v>
+        <v>6962621</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839407</v>
+        <v>119839410</v>
       </c>
       <c r="B3" t="n">
-        <v>90598</v>
+        <v>57320</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548281</v>
+        <v>548277</v>
       </c>
       <c r="R3" t="n">
-        <v>6962549</v>
+        <v>6962656</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -853,6 +853,11 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -879,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839408</v>
+        <v>119839411</v>
       </c>
       <c r="B4" t="n">
-        <v>79659</v>
+        <v>90864</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -891,25 +896,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>6464</v>
+        <v>658</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -919,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548269</v>
+        <v>548284</v>
       </c>
       <c r="R4" t="n">
-        <v>6962621</v>
+        <v>6962633</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -981,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839410</v>
+        <v>119839413</v>
       </c>
       <c r="B5" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -997,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1024,7 +1029,7 @@
         <v>548277</v>
       </c>
       <c r="R5" t="n">
-        <v>6962656</v>
+        <v>6962630</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1057,11 +1062,6 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839409</v>
+        <v>119839407</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>90598</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>5432</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548269</v>
+        <v>548281</v>
       </c>
       <c r="R6" t="n">
-        <v>6962621</v>
+        <v>6962549</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839413</v>
+        <v>119839408</v>
       </c>
       <c r="B7" t="n">
-        <v>90580</v>
+        <v>79659</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>1202</v>
+        <v>6464</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1230,10 +1230,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>548277</v>
+        <v>548269</v>
       </c>
       <c r="R7" t="n">
-        <v>6962630</v>
+        <v>6962621</v>
       </c>
       <c r="S7" t="n">
         <v>25</v>

--- a/artfynd/A 45937-2023 artfynd.xlsx
+++ b/artfynd/A 45937-2023 artfynd.xlsx
@@ -884,10 +884,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839411</v>
+        <v>119839413</v>
       </c>
       <c r="B4" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +900,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>548284</v>
+        <v>548277</v>
       </c>
       <c r="R4" t="n">
-        <v>6962633</v>
+        <v>6962630</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839413</v>
+        <v>119839411</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548277</v>
+        <v>548284</v>
       </c>
       <c r="R5" t="n">
-        <v>6962630</v>
+        <v>6962633</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>

--- a/artfynd/A 45937-2023 artfynd.xlsx
+++ b/artfynd/A 45937-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>119839409</v>
+        <v>119839408</v>
       </c>
       <c r="B2" t="n">
-        <v>79623</v>
+        <v>79659</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,25 +687,25 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6464</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Luddlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma resupinatum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>119839410</v>
+        <v>119839407</v>
       </c>
       <c r="B3" t="n">
-        <v>57320</v>
+        <v>90598</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -793,21 +793,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>5432</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Granticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea chrysoloma</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -817,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>548277</v>
+        <v>548281</v>
       </c>
       <c r="R3" t="n">
-        <v>6962656</v>
+        <v>6962549</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -853,11 +853,6 @@
       <c r="AA3" t="inlineStr">
         <is>
           <t>2024-09-11</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -884,10 +879,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>119839413</v>
+        <v>119839410</v>
       </c>
       <c r="B4" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -900,21 +895,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -927,7 +922,7 @@
         <v>548277</v>
       </c>
       <c r="R4" t="n">
-        <v>6962630</v>
+        <v>6962656</v>
       </c>
       <c r="S4" t="n">
         <v>25</v>
@@ -960,6 +955,11 @@
       <c r="AA4" t="inlineStr">
         <is>
           <t>2024-09-11</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>färska ringhack</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -986,10 +986,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>119839411</v>
+        <v>119839413</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1002,21 +1002,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1026,10 +1026,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>548284</v>
+        <v>548277</v>
       </c>
       <c r="R5" t="n">
-        <v>6962633</v>
+        <v>6962630</v>
       </c>
       <c r="S5" t="n">
         <v>25</v>
@@ -1088,10 +1088,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>119839407</v>
+        <v>119839411</v>
       </c>
       <c r="B6" t="n">
-        <v>90598</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1104,21 +1104,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>5432</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1128,10 +1128,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>548281</v>
+        <v>548284</v>
       </c>
       <c r="R6" t="n">
-        <v>6962549</v>
+        <v>6962633</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1190,10 +1190,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>119839408</v>
+        <v>119839409</v>
       </c>
       <c r="B7" t="n">
-        <v>79659</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1202,25 +1202,25 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6464</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Luddlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Nephroma resupinatum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
